--- a/templates/任课总表_模板.xlsx
+++ b/templates/任课总表_模板.xlsx
@@ -779,7 +779,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>11. 没填的班级，运行程序时会逐个问你。</t>
+          <t>11. 应考人数可以不填：没填的班按实考人数算（参考率按 100%）。</t>
         </is>
       </c>
     </row>
